--- a/output/pdf_financials_xlsx/CZ.H.xlsx
+++ b/output/pdf_financials_xlsx/CZ.H.xlsx
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.000833</v>
       </c>
       <c r="L103" s="3" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0.01479</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.015374</v>
+        <v>0.016207</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0.017927</v>
@@ -10468,7 +10468,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -19180,7 +19184,7 @@
         <v>-4.95438</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.966368</v>
+        <v>-0.966368</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CZ.H.xlsx
+++ b/output/pdf_financials_xlsx/CZ.H.xlsx
@@ -1903,40 +1903,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.06568499999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.060995</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000869</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.015059</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001376</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002514</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001857</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000626</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000218</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000415</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.002887</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="35">
@@ -1989,40 +1989,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.06568499999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.060995</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000869</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.015059</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001376</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002514</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001857</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000626</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000218</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000415</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.002887</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="37">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.071878</v>
+        <v>0.006193</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.06668</v>
+        <v>0.005685</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">

--- a/output/pdf_financials_xlsx/CZ.H.xlsx
+++ b/output/pdf_financials_xlsx/CZ.H.xlsx
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.254181</v>
+        <v>-0.254181</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0.261033</v>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001473</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001473</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.04052</v>
+        <v>-0.041993</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.242086</v>
@@ -11866,7 +11866,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -12780,7 +12784,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
         <v>-0.254181</v>
       </c>
@@ -13006,7 +13014,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>-0.001473</v>
       </c>
@@ -20022,7 +20034,11 @@
           <t>Deferred Income tax recovery</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="n">
         <v>0.254181</v>
       </c>
